--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N36_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0001T0006Z000C1N36_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>28.68270404508383</v>
+        <v>4.660939407326123</v>
       </c>
       <c r="D2" t="n">
-        <v>28.82532455954629</v>
+        <v>4.684115240926272</v>
       </c>
       <c r="E2" t="n">
-        <v>7.86551276570788</v>
+        <v>1.278145824427531</v>
       </c>
       <c r="F2" t="n">
-        <v>8.384809418021211</v>
+        <v>1.362531530428447</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>26.0995232213594</v>
+        <v>4.241172523470903</v>
       </c>
       <c r="D3" t="n">
-        <v>24.71205265732543</v>
+        <v>4.015708556815383</v>
       </c>
       <c r="E3" t="n">
-        <v>7.86551276570788</v>
+        <v>1.278145824427531</v>
       </c>
       <c r="F3" t="n">
-        <v>8.384809418021211</v>
+        <v>1.362531530428447</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>17.03492109174372</v>
+        <v>2.768174677408355</v>
       </c>
       <c r="D4" t="n">
-        <v>12.89116414639598</v>
+        <v>2.094814173789346</v>
       </c>
       <c r="E4" t="n">
-        <v>7.86551276570788</v>
+        <v>1.278145824427531</v>
       </c>
       <c r="F4" t="n">
-        <v>8.384809418021211</v>
+        <v>1.362531530428447</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>8.901089703926353</v>
+        <v>1.446427076888032</v>
       </c>
       <c r="D5" t="n">
-        <v>7.644725226583763</v>
+        <v>1.242267849319862</v>
       </c>
       <c r="E5" t="n">
-        <v>7.86551276570788</v>
+        <v>1.278145824427531</v>
       </c>
       <c r="F5" t="n">
-        <v>8.384809418021211</v>
+        <v>1.362531530428447</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>32.93161194371275</v>
+        <v>5.351386940853322</v>
       </c>
       <c r="D6" t="n">
-        <v>32.12397753634852</v>
+        <v>5.220146349656635</v>
       </c>
       <c r="E6" t="n">
-        <v>7.86551276570788</v>
+        <v>1.278145824427531</v>
       </c>
       <c r="F6" t="n">
-        <v>8.384809418021211</v>
+        <v>1.362531530428447</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>16.97078405194848</v>
+        <v>2.757752408441628</v>
       </c>
       <c r="D7" t="n">
-        <v>17.13170258319586</v>
+        <v>2.783901669769328</v>
       </c>
       <c r="E7" t="n">
-        <v>7.86551276570788</v>
+        <v>1.278145824427531</v>
       </c>
       <c r="F7" t="n">
-        <v>8.384809418021211</v>
+        <v>1.362531530428447</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>24.5255339650369</v>
+        <v>3.985399269318497</v>
       </c>
       <c r="D8" t="n">
-        <v>26.11650875415508</v>
+        <v>4.243932672550201</v>
       </c>
       <c r="E8" t="n">
-        <v>7.86551276570788</v>
+        <v>1.278145824427531</v>
       </c>
       <c r="F8" t="n">
-        <v>8.384809418021211</v>
+        <v>1.362531530428447</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>9.327781694372376</v>
+        <v>1.515764525335511</v>
       </c>
       <c r="D9" t="n">
-        <v>9.357999597991167</v>
+        <v>1.520674934673565</v>
       </c>
       <c r="E9" t="n">
-        <v>7.86551276570788</v>
+        <v>1.278145824427531</v>
       </c>
       <c r="F9" t="n">
-        <v>8.384809418021211</v>
+        <v>1.362531530428447</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>9.609692862676717</v>
+        <v>1.561575090184967</v>
       </c>
       <c r="D10" t="n">
-        <v>14.22484302798871</v>
+        <v>2.311536992048166</v>
       </c>
       <c r="E10" t="n">
-        <v>7.86551276570788</v>
+        <v>1.278145824427531</v>
       </c>
       <c r="F10" t="n">
-        <v>8.384809418021211</v>
+        <v>1.362531530428447</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>17.69348191152701</v>
+        <v>2.875190810623139</v>
       </c>
       <c r="D11" t="n">
-        <v>16.18036852699538</v>
+        <v>2.629309885636749</v>
       </c>
       <c r="E11" t="n">
-        <v>7.86551276570788</v>
+        <v>1.278145824427531</v>
       </c>
       <c r="F11" t="n">
-        <v>8.384809418021211</v>
+        <v>1.362531530428447</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>8.883170973654241</v>
+        <v>1.443515283218814</v>
       </c>
       <c r="D12" t="n">
-        <v>8.167120614214152</v>
+        <v>1.3271570998098</v>
       </c>
       <c r="E12" t="n">
-        <v>7.86551276570788</v>
+        <v>1.278145824427531</v>
       </c>
       <c r="F12" t="n">
-        <v>8.384809418021211</v>
+        <v>1.362531530428447</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>16.91290936776418</v>
+        <v>2.748347772261678</v>
       </c>
       <c r="D13" t="n">
-        <v>16.53571052344918</v>
+        <v>2.687052960060492</v>
       </c>
       <c r="E13" t="n">
-        <v>7.86551276570788</v>
+        <v>1.278145824427531</v>
       </c>
       <c r="F13" t="n">
-        <v>8.384809418021211</v>
+        <v>1.362531530428447</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>11.19316851487161</v>
+        <v>1.818889883666636</v>
       </c>
       <c r="D14" t="n">
-        <v>4.59621551532838</v>
+        <v>0.7468850212408618</v>
       </c>
       <c r="E14" t="n">
-        <v>7.86551276570788</v>
+        <v>1.278145824427531</v>
       </c>
       <c r="F14" t="n">
-        <v>8.384809418021211</v>
+        <v>1.362531530428447</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
